--- a/KatalonData/EmailTextToPay/BillFileLookUp_SearchButton_Demo.xlsx
+++ b/KatalonData/EmailTextToPay/BillFileLookUp_SearchButton_Demo.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="29">
   <si>
     <t>Result</t>
   </si>
@@ -111,6 +111,18 @@
   </si>
   <si>
     <t>Wed Mar 11 16:53:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Mar 19 22:35:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 25 17:55:10 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 25 17:56:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 25 17:57:06 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -583,7 +595,7 @@
         <v>18</v>
       </c>
       <c r="B2" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>9</v>
@@ -599,7 +611,7 @@
         <v>18</v>
       </c>
       <c r="B3" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>10</v>
@@ -617,7 +629,7 @@
         <v>18</v>
       </c>
       <c r="B4" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>11</v>

--- a/KatalonData/EmailTextToPay/BillFileLookUp_SearchButton_Demo.xlsx
+++ b/KatalonData/EmailTextToPay/BillFileLookUp_SearchButton_Demo.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="35">
   <si>
     <t>Result</t>
   </si>
@@ -123,6 +123,24 @@
   </si>
   <si>
     <t>Wed Mar 25 17:57:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 23:04:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 23:05:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 23:06:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 02:05:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 02:06:13 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 02:06:54 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -595,7 +613,7 @@
         <v>18</v>
       </c>
       <c r="B2" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>9</v>
@@ -611,7 +629,7 @@
         <v>18</v>
       </c>
       <c r="B3" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>10</v>
@@ -629,7 +647,7 @@
         <v>18</v>
       </c>
       <c r="B4" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>11</v>

--- a/KatalonData/EmailTextToPay/BillFileLookUp_SearchButton_Demo.xlsx
+++ b/KatalonData/EmailTextToPay/BillFileLookUp_SearchButton_Demo.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="38">
   <si>
     <t>Result</t>
   </si>
@@ -141,6 +141,15 @@
   </si>
   <si>
     <t>Thu Jun 18 02:06:54 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 29 13:44:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 29 13:45:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 29 13:45:56 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -613,7 +622,7 @@
         <v>18</v>
       </c>
       <c r="B2" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>9</v>
@@ -629,7 +638,7 @@
         <v>18</v>
       </c>
       <c r="B3" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>10</v>
@@ -647,7 +656,7 @@
         <v>18</v>
       </c>
       <c r="B4" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>11</v>

--- a/KatalonData/EmailTextToPay/BillFileLookUp_SearchButton_Demo.xlsx
+++ b/KatalonData/EmailTextToPay/BillFileLookUp_SearchButton_Demo.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="44">
   <si>
     <t>Result</t>
   </si>
@@ -150,6 +150,24 @@
   </si>
   <si>
     <t>Mon Jun 29 13:45:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 14:42:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 14:43:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 14:44:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 18:08:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 18:09:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 18:09:45 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -565,7 +583,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F033DD18-DD0F-43E3-A2D0-6223D1731E2C}">
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:L4"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" customWidth="true" width="6.36328125" collapsed="true"/>
@@ -618,11 +636,11 @@
       </c>
     </row>
     <row customFormat="1" ht="13" r="2" s="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>18</v>
       </c>
-      <c r="B2" t="s">
-        <v>35</v>
+      <c r="B2" t="s" s="0">
+        <v>41</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>9</v>
@@ -634,11 +652,11 @@
       <c r="L2" s="3"/>
     </row>
     <row customFormat="1" ht="13" r="3" s="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="A3" t="s" s="0">
         <v>18</v>
       </c>
-      <c r="B3" t="s">
-        <v>36</v>
+      <c r="B3" t="s" s="0">
+        <v>42</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>10</v>
@@ -652,11 +670,11 @@
       <c r="L3" s="3"/>
     </row>
     <row customFormat="1" ht="13" r="4" s="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="A4" t="s" s="0">
         <v>18</v>
       </c>
-      <c r="B4" t="s">
-        <v>37</v>
+      <c r="B4" t="s" s="0">
+        <v>43</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>11</v>
